--- a/artfynd/A 33674-2025 artfynd.xlsx
+++ b/artfynd/A 33674-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132260035</v>
+        <v>132260010</v>
       </c>
       <c r="B2" t="n">
-        <v>80463</v>
+        <v>90997</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599568</v>
+        <v>599646</v>
       </c>
       <c r="R2" t="n">
-        <v>7069940</v>
+        <v>7069947</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132260068</v>
+        <v>132260100</v>
       </c>
       <c r="B3" t="n">
-        <v>80434</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599587</v>
+        <v>599549</v>
       </c>
       <c r="R3" t="n">
-        <v>7069937</v>
+        <v>7069919</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132260100</v>
+        <v>132260084</v>
       </c>
       <c r="B4" t="n">
-        <v>79329</v>
+        <v>79130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599549</v>
+        <v>599564</v>
       </c>
       <c r="R4" t="n">
-        <v>7069919</v>
+        <v>7069879</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132260037</v>
+        <v>132260085</v>
       </c>
       <c r="B5" t="n">
-        <v>80338</v>
+        <v>79130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599583</v>
+        <v>599618</v>
       </c>
       <c r="R5" t="n">
-        <v>7069934</v>
+        <v>7069909</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132260070</v>
+        <v>132260037</v>
       </c>
       <c r="B6" t="n">
-        <v>80434</v>
+        <v>80382</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599572</v>
+        <v>599583</v>
       </c>
       <c r="R6" t="n">
-        <v>7069919</v>
+        <v>7069934</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1173,6 +1173,511 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132260068</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Degerforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>599587</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7069937</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Maya Edlund, Gunnar Gredeby, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132260070</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Degerforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>599572</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7069919</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Maya Edlund, Gunnar Gredeby, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132260035</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Degerforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>599568</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7069940</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Maya Edlund, Gunnar Gredeby, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132260047</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5484</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>101920</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Raggbock</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tragosoma depsarium</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1767)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Degerforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>599568</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7069880</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Maya Edlund, Gunnar Gredeby, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132260009</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Degerforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>599609</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7069904</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Maya Edlund, Gunnar Gredeby, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Naturvärdesinventering (NVI)</t>
         </is>

--- a/artfynd/A 33674-2025 artfynd.xlsx
+++ b/artfynd/A 33674-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132260010</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132260100</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132260084</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132260085</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132260037</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132260068</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132260070</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132260035</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132260047</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,8 +1732,25 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132260009</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>